--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/135.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/135.xlsx
@@ -426,13 +426,13 @@
         <v>-17.85871551505875</v>
       </c>
       <c r="E2">
-        <v>-11.92553912305115</v>
+        <v>-13.94225426610108</v>
       </c>
       <c r="F2">
-        <v>-0.8484489173431972</v>
+        <v>-2.103643547331209</v>
       </c>
       <c r="G2">
-        <v>-4.950594260640006</v>
+        <v>-9.229510786148948</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-17.5288444680404</v>
       </c>
       <c r="E3">
-        <v>-12.80410383680527</v>
+        <v>-15.63815872502561</v>
       </c>
       <c r="F3">
-        <v>-1.290875377439234</v>
+        <v>-2.43579577268224</v>
       </c>
       <c r="G3">
-        <v>-4.99232368716252</v>
+        <v>-8.222869893477219</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.16122303591636</v>
       </c>
       <c r="E4">
-        <v>-14.02103159993851</v>
+        <v>-14.22846740880786</v>
       </c>
       <c r="F4">
-        <v>-0.7850428754597057</v>
+        <v>-1.9914047253981</v>
       </c>
       <c r="G4">
-        <v>-3.688925492350521</v>
+        <v>-9.017533244723873</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.77217957184024</v>
       </c>
       <c r="E5">
-        <v>-13.45590521462529</v>
+        <v>-16.17985478582314</v>
       </c>
       <c r="F5">
-        <v>-1.019043342995461</v>
+        <v>-1.988609484457349</v>
       </c>
       <c r="G5">
-        <v>-4.516343381162726</v>
+        <v>-8.170106418672315</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.34044472360619</v>
       </c>
       <c r="E6">
-        <v>-13.8015817495268</v>
+        <v>-16.32645960334746</v>
       </c>
       <c r="F6">
-        <v>-0.9116031499861338</v>
+        <v>-2.247720401135355</v>
       </c>
       <c r="G6">
-        <v>-3.003500212263197</v>
+        <v>-8.026802833913882</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-15.86971701819157</v>
       </c>
       <c r="E7">
-        <v>-14.93296211018114</v>
+        <v>-17.64950762637644</v>
       </c>
       <c r="F7">
-        <v>-1.028033249624453</v>
+        <v>-2.25439651342189</v>
       </c>
       <c r="G7">
-        <v>-4.020023083369651</v>
+        <v>-6.970632869429117</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.34990445508533</v>
       </c>
       <c r="E8">
-        <v>-15.43039233755369</v>
+        <v>-17.77888160030158</v>
       </c>
       <c r="F8">
-        <v>-0.5867573518759829</v>
+        <v>-2.493772870687605</v>
       </c>
       <c r="G8">
-        <v>-2.657700488504164</v>
+        <v>-5.770901097633857</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-14.79785430121804</v>
       </c>
       <c r="E9">
-        <v>-15.11800008660856</v>
+        <v>-18.76206764905491</v>
       </c>
       <c r="F9">
-        <v>-0.8517066004112561</v>
+        <v>-1.928481713818818</v>
       </c>
       <c r="G9">
-        <v>-3.053519244816045</v>
+        <v>-5.673183724951189</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-14.22103326995876</v>
       </c>
       <c r="E10">
-        <v>-17.5133952831279</v>
+        <v>-18.61780858106656</v>
       </c>
       <c r="F10">
-        <v>-1.191733803426809</v>
+        <v>-2.155629485858467</v>
       </c>
       <c r="G10">
-        <v>-1.912552966888388</v>
+        <v>-5.662725711592631</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-13.64918124410494</v>
       </c>
       <c r="E11">
-        <v>-17.52559499210456</v>
+        <v>-20.27593650981911</v>
       </c>
       <c r="F11">
-        <v>-1.218533274927876</v>
+        <v>-2.068395796624231</v>
       </c>
       <c r="G11">
-        <v>-2.544410309604765</v>
+        <v>-6.606214637557223</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-13.10996631240538</v>
       </c>
       <c r="E12">
-        <v>-16.64662724416376</v>
+        <v>-19.97428579922017</v>
       </c>
       <c r="F12">
-        <v>-0.6822730311950091</v>
+        <v>-2.416245715009098</v>
       </c>
       <c r="G12">
-        <v>-1.038694745251287</v>
+        <v>-4.891593718039116</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-12.63135517164299</v>
       </c>
       <c r="E13">
-        <v>-17.82994014473806</v>
+        <v>-21.29213966256236</v>
       </c>
       <c r="F13">
-        <v>-0.5832193528608911</v>
+        <v>-1.435929377793207</v>
       </c>
       <c r="G13">
-        <v>-0.7549346448981962</v>
+        <v>-5.346939393692631</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-12.24959479435682</v>
       </c>
       <c r="E14">
-        <v>-19.43388488198883</v>
+        <v>-22.74500997844324</v>
       </c>
       <c r="F14">
-        <v>-0.7486580239054421</v>
+        <v>-1.321354589634824</v>
       </c>
       <c r="G14">
-        <v>-1.448235712823447</v>
+        <v>-4.611276585046867</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-11.97889231704933</v>
       </c>
       <c r="E15">
-        <v>-19.32143834390437</v>
+        <v>-22.63893500328757</v>
       </c>
       <c r="F15">
-        <v>-0.5281681515343005</v>
+        <v>-1.021735643051708</v>
       </c>
       <c r="G15">
-        <v>-0.1844117793878961</v>
+        <v>-4.778346576231726</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-11.83451943773486</v>
       </c>
       <c r="E16">
-        <v>-19.60579481226802</v>
+        <v>-23.49981149756773</v>
       </c>
       <c r="F16">
-        <v>-0.1893287279553267</v>
+        <v>-1.431109368839567</v>
       </c>
       <c r="G16">
-        <v>0.2541394987448973</v>
+        <v>-4.179680763092082</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-11.80270176585807</v>
       </c>
       <c r="E17">
-        <v>-21.50414017323144</v>
+        <v>-25.71455680897308</v>
       </c>
       <c r="F17">
-        <v>0.05849986778108838</v>
+        <v>-1.61043080593886</v>
       </c>
       <c r="G17">
-        <v>-0.2989599655922184</v>
+        <v>-2.735898884687289</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-11.86810148404773</v>
       </c>
       <c r="E18">
-        <v>-22.0065924782785</v>
+        <v>-26.31369203408389</v>
       </c>
       <c r="F18">
-        <v>-0.01297040462382073</v>
+        <v>-0.757029493374455</v>
       </c>
       <c r="G18">
-        <v>0.02284823464371582</v>
+        <v>-3.285333575112432</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-11.99982357325449</v>
       </c>
       <c r="E19">
-        <v>-23.13744300747394</v>
+        <v>-25.44020373969238</v>
       </c>
       <c r="F19">
-        <v>0.657695792740561</v>
+        <v>-0.5590575435619892</v>
       </c>
       <c r="G19">
-        <v>0.1108094296221513</v>
+        <v>-4.137024383818573</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-12.162615425799</v>
       </c>
       <c r="E20">
-        <v>-22.88995284600674</v>
+        <v>-26.21393428016892</v>
       </c>
       <c r="F20">
-        <v>1.191426858126471</v>
+        <v>0.1183980010618814</v>
       </c>
       <c r="G20">
-        <v>0.3813935587289425</v>
+        <v>-3.623214473941527</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-12.33033512089458</v>
       </c>
       <c r="E21">
-        <v>-23.81756999021195</v>
+        <v>-26.5582341589721</v>
       </c>
       <c r="F21">
-        <v>0.9826247354112725</v>
+        <v>-0.3402004719896657</v>
       </c>
       <c r="G21">
-        <v>0.03767616811411147</v>
+        <v>-2.828114130683688</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-12.471663768029</v>
       </c>
       <c r="E22">
-        <v>-25.16822359079169</v>
+        <v>-26.9934657958493</v>
       </c>
       <c r="F22">
-        <v>1.89713254886995</v>
+        <v>0.1373327889868755</v>
       </c>
       <c r="G22">
-        <v>-0.1077064392429827</v>
+        <v>-1.322984532890661</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-12.57319181028685</v>
       </c>
       <c r="E23">
-        <v>-24.27003699916234</v>
+        <v>-27.94137956055688</v>
       </c>
       <c r="F23">
-        <v>1.577743409491446</v>
+        <v>0.2568598255428369</v>
       </c>
       <c r="G23">
-        <v>0.2914261731537087</v>
+        <v>-2.299032674233985</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-12.6170764328779</v>
       </c>
       <c r="E24">
-        <v>-24.09736175677586</v>
+        <v>-29.15537287253315</v>
       </c>
       <c r="F24">
-        <v>1.919868230991999</v>
+        <v>0.3741031581687346</v>
       </c>
       <c r="G24">
-        <v>0.9634967125356131</v>
+        <v>-3.430722803560604</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-12.60127587067517</v>
       </c>
       <c r="E25">
-        <v>-24.62747398106177</v>
+        <v>-29.1099432212882</v>
       </c>
       <c r="F25">
-        <v>2.107873127625647</v>
+        <v>0.5589200547946027</v>
       </c>
       <c r="G25">
-        <v>0.2206963677071798</v>
+        <v>-3.232669416673706</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-12.52300307421959</v>
       </c>
       <c r="E26">
-        <v>-25.84605916568182</v>
+        <v>-29.60311215461953</v>
       </c>
       <c r="F26">
-        <v>1.883062905517186</v>
+        <v>0.5422396722402367</v>
       </c>
       <c r="G26">
-        <v>0.3276302991711784</v>
+        <v>-3.201878032612944</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-12.38606121085925</v>
       </c>
       <c r="E27">
-        <v>-26.66413252364147</v>
+        <v>-30.41912732114271</v>
       </c>
       <c r="F27">
-        <v>1.93390778393237</v>
+        <v>0.4687066228804677</v>
       </c>
       <c r="G27">
-        <v>0.2004854871899292</v>
+        <v>-2.850198779976166</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-12.20396772409108</v>
       </c>
       <c r="E28">
-        <v>-24.38734258985703</v>
+        <v>-29.41143090682286</v>
       </c>
       <c r="F28">
-        <v>1.808416510898863</v>
+        <v>-0.1110691082909287</v>
       </c>
       <c r="G28">
-        <v>0.198932841332011</v>
+        <v>-3.949783238662934</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-11.98598369822386</v>
       </c>
       <c r="E29">
-        <v>-25.11414002571809</v>
+        <v>-28.90370745803088</v>
       </c>
       <c r="F29">
-        <v>2.094923164355099</v>
+        <v>0.6726538951118866</v>
       </c>
       <c r="G29">
-        <v>0.1374195946668131</v>
+        <v>-3.433351376718786</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-11.7538002383692</v>
       </c>
       <c r="E30">
-        <v>-25.33656508355283</v>
+        <v>-29.14664197464636</v>
       </c>
       <c r="F30">
-        <v>1.711913390941561</v>
+        <v>0.3610407517781901</v>
       </c>
       <c r="G30">
-        <v>-0.03849286365344001</v>
+        <v>-2.426912427324952</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-11.52067084719879</v>
       </c>
       <c r="E31">
-        <v>-24.17687270340254</v>
+        <v>-28.27564886943307</v>
       </c>
       <c r="F31">
-        <v>1.78117518544739</v>
+        <v>0.569937896848315</v>
       </c>
       <c r="G31">
-        <v>0.2362658633783722</v>
+        <v>-2.945774229694925</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-11.30672279724463</v>
       </c>
       <c r="E32">
-        <v>-23.6897221120274</v>
+        <v>-26.89603114910026</v>
       </c>
       <c r="F32">
-        <v>1.695628143013097</v>
+        <v>0.4498272646625141</v>
       </c>
       <c r="G32">
-        <v>0.08361660856257773</v>
+        <v>-3.330347062809902</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-11.12343336372289</v>
       </c>
       <c r="E33">
-        <v>-23.69260674997028</v>
+        <v>-27.46874725685033</v>
       </c>
       <c r="F33">
-        <v>1.300767498234326</v>
+        <v>0.6150497598496076</v>
       </c>
       <c r="G33">
-        <v>-0.8345002963890399</v>
+        <v>-2.669625073536619</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.97763390084466</v>
       </c>
       <c r="E34">
-        <v>-23.20449159363151</v>
+        <v>-27.95502385274199</v>
       </c>
       <c r="F34">
-        <v>1.331074878338091</v>
+        <v>0.5047779006634743</v>
       </c>
       <c r="G34">
-        <v>0.4799551205241243</v>
+        <v>-3.527880694047135</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.87538191705462</v>
       </c>
       <c r="E35">
-        <v>-23.52170214092081</v>
+        <v>-26.73976256804357</v>
       </c>
       <c r="F35">
-        <v>1.389160460198663</v>
+        <v>-0.02878054077765273</v>
       </c>
       <c r="G35">
-        <v>-0.814958146070722</v>
+        <v>-3.702836404706539</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-10.80862630989456</v>
       </c>
       <c r="E36">
-        <v>-22.01819895716016</v>
+        <v>-26.76033089698641</v>
       </c>
       <c r="F36">
-        <v>1.302424054621875</v>
+        <v>0.5684270414049857</v>
       </c>
       <c r="G36">
-        <v>-0.2561877172248347</v>
+        <v>-3.468059136152505</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-10.77735647013936</v>
       </c>
       <c r="E37">
-        <v>-21.95584639854855</v>
+        <v>-24.35938831980768</v>
       </c>
       <c r="F37">
-        <v>1.186754925675925</v>
+        <v>-0.04160380757496594</v>
       </c>
       <c r="G37">
-        <v>-0.0818212836714213</v>
+        <v>-2.97891279054303</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-10.77014410954352</v>
       </c>
       <c r="E38">
-        <v>-21.07931949809788</v>
+        <v>-25.56513528061598</v>
       </c>
       <c r="F38">
-        <v>1.755596751207127</v>
+        <v>-0.2554634951311203</v>
       </c>
       <c r="G38">
-        <v>0.8183259800930323</v>
+        <v>-3.091524307606878</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.78228146405107</v>
       </c>
       <c r="E39">
-        <v>-20.48306438245594</v>
+        <v>-24.16470016526992</v>
       </c>
       <c r="F39">
-        <v>1.046022066912229</v>
+        <v>0.2245403470735064</v>
       </c>
       <c r="G39">
-        <v>-0.4759351090305776</v>
+        <v>-2.442697108456197</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-10.80497830563398</v>
       </c>
       <c r="E40">
-        <v>-20.84321844875997</v>
+        <v>-25.51224270420639</v>
       </c>
       <c r="F40">
-        <v>1.556661116345116</v>
+        <v>-0.01049428042503115</v>
       </c>
       <c r="G40">
-        <v>-0.07614700861711049</v>
+        <v>-2.161499370350502</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-10.83327944997426</v>
       </c>
       <c r="E41">
-        <v>-19.48003908907501</v>
+        <v>-24.77074584171644</v>
       </c>
       <c r="F41">
-        <v>1.897104042163473</v>
+        <v>0.3979680226084917</v>
       </c>
       <c r="G41">
-        <v>0.07292685701627107</v>
+        <v>-2.85476733282036</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-10.86871660592946</v>
       </c>
       <c r="E42">
-        <v>-19.42185725502446</v>
+        <v>-23.33639245605292</v>
       </c>
       <c r="F42">
-        <v>1.048666855791013</v>
+        <v>0.01181063368801803</v>
       </c>
       <c r="G42">
-        <v>-0.2527944080470818</v>
+        <v>-1.853118742821852</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-10.90659034369328</v>
       </c>
       <c r="E43">
-        <v>-18.00583060366998</v>
+        <v>-23.16309228425339</v>
       </c>
       <c r="F43">
-        <v>1.443212343092612</v>
+        <v>-0.2615393828757038</v>
       </c>
       <c r="G43">
-        <v>0.1859720555457643</v>
+        <v>-3.280092981523765</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-10.95255706851425</v>
       </c>
       <c r="E44">
-        <v>-17.39973964248339</v>
+        <v>-23.54333918972945</v>
       </c>
       <c r="F44">
-        <v>1.493989122153431</v>
+        <v>0.06815572274752268</v>
       </c>
       <c r="G44">
-        <v>0.1312255639628367</v>
+        <v>-3.044226543487311</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-11.00097779048096</v>
       </c>
       <c r="E45">
-        <v>-17.45255523483484</v>
+        <v>-22.85266539102759</v>
       </c>
       <c r="F45">
-        <v>1.665675513034391</v>
+        <v>0.4702436094714017</v>
       </c>
       <c r="G45">
-        <v>-0.546744367570049</v>
+        <v>-2.887932378032779</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-11.05445211160121</v>
       </c>
       <c r="E46">
-        <v>-16.75122140831892</v>
+        <v>-22.43527594174061</v>
       </c>
       <c r="F46">
-        <v>1.508171208626191</v>
+        <v>0.05194015787933819</v>
       </c>
       <c r="G46">
-        <v>-0.3130330946796603</v>
+        <v>-2.521114000644914</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-11.11152964865887</v>
       </c>
       <c r="E47">
-        <v>-16.19802302354191</v>
+        <v>-19.41221613386213</v>
       </c>
       <c r="F47">
-        <v>1.220345328142395</v>
+        <v>-0.2704223893554036</v>
       </c>
       <c r="G47">
-        <v>0.3142259002826693</v>
+        <v>-2.900111875071758</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-11.17547583108116</v>
       </c>
       <c r="E48">
-        <v>-15.45330641603251</v>
+        <v>-21.58342922463175</v>
       </c>
       <c r="F48">
-        <v>1.563705440256991</v>
+        <v>0.590206165154109</v>
       </c>
       <c r="G48">
-        <v>0.1942384877573244</v>
+        <v>-3.063589924346508</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-11.25247791093895</v>
       </c>
       <c r="E49">
-        <v>-14.69443379877512</v>
+        <v>-20.46252322435715</v>
       </c>
       <c r="F49">
-        <v>1.469717245293406</v>
+        <v>-0.5159181862783764</v>
       </c>
       <c r="G49">
-        <v>0.2638460182660404</v>
+        <v>-3.406688242945496</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-11.33970394589082</v>
       </c>
       <c r="E50">
-        <v>-14.44599265776631</v>
+        <v>-20.13944377475391</v>
       </c>
       <c r="F50">
-        <v>1.390847106998606</v>
+        <v>-0.1309169026761736</v>
       </c>
       <c r="G50">
-        <v>-0.2690657393725996</v>
+        <v>-3.434659042206798</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-11.44315207452508</v>
       </c>
       <c r="E51">
-        <v>-14.82322359955327</v>
+        <v>-19.03623505090129</v>
       </c>
       <c r="F51">
-        <v>1.3846611516929</v>
+        <v>0.8251726932982826</v>
       </c>
       <c r="G51">
-        <v>-0.2161168740174963</v>
+        <v>-3.426101281987782</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-11.5570528473843</v>
       </c>
       <c r="E52">
-        <v>-14.18959951640003</v>
+        <v>-20.23544742371653</v>
       </c>
       <c r="F52">
-        <v>1.378696915215355</v>
+        <v>0.0275392089872049</v>
       </c>
       <c r="G52">
-        <v>0.2363718008356288</v>
+        <v>-2.806741248682153</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.68226085367479</v>
       </c>
       <c r="E53">
-        <v>-14.09303433666047</v>
+        <v>-18.40508351455624</v>
       </c>
       <c r="F53">
-        <v>1.504793163908559</v>
+        <v>0.2049095203986767</v>
       </c>
       <c r="G53">
-        <v>0.6621675470056104</v>
+        <v>-1.794584987141998</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.81396359645586</v>
       </c>
       <c r="E54">
-        <v>-13.22374393767406</v>
+        <v>-19.51471361455174</v>
       </c>
       <c r="F54">
-        <v>1.40169074140162</v>
+        <v>0.2053094061423252</v>
       </c>
       <c r="G54">
-        <v>-0.4013253442120228</v>
+        <v>-3.777244226247198</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.94882242861691</v>
       </c>
       <c r="E55">
-        <v>-13.10415146760549</v>
+        <v>-16.73632272883368</v>
       </c>
       <c r="F55">
-        <v>1.347413972267679</v>
+        <v>0.4772475488824326</v>
       </c>
       <c r="G55">
-        <v>-0.5767710156112387</v>
+        <v>-2.316379932859766</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.08796361185068</v>
       </c>
       <c r="E56">
-        <v>-11.85581873722906</v>
+        <v>-16.33817929407931</v>
       </c>
       <c r="F56">
-        <v>1.36914875225117</v>
+        <v>-0.2725920664595556</v>
       </c>
       <c r="G56">
-        <v>-0.6712904013029704</v>
+        <v>-2.065357817344528</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-12.22508637027764</v>
       </c>
       <c r="E57">
-        <v>-12.82955838920238</v>
+        <v>-16.50729062742175</v>
       </c>
       <c r="F57">
-        <v>1.350746089513764</v>
+        <v>-0.05580014740096514</v>
       </c>
       <c r="G57">
-        <v>-0.4415186776043143</v>
+        <v>-3.873253357431602</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.36566052981083</v>
       </c>
       <c r="E58">
-        <v>-12.46461772587225</v>
+        <v>-16.49466977036237</v>
       </c>
       <c r="F58">
-        <v>1.217526331612913</v>
+        <v>0.1535950731795654</v>
       </c>
       <c r="G58">
-        <v>-0.7609068690510413</v>
+        <v>-3.70351506654209</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.50423642195887</v>
       </c>
       <c r="E59">
-        <v>-12.02409683135409</v>
+        <v>-17.07326836584841</v>
       </c>
       <c r="F59">
-        <v>1.656621466315823</v>
+        <v>0.1459354795195426</v>
       </c>
       <c r="G59">
-        <v>-0.3331281061030364</v>
+        <v>-3.582167019800104</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-12.64190735728119</v>
       </c>
       <c r="E60">
-        <v>-11.79521869805841</v>
+        <v>-14.91981595013688</v>
       </c>
       <c r="F60">
-        <v>1.304364094368289</v>
+        <v>0.3117463214542218</v>
       </c>
       <c r="G60">
-        <v>-1.381889069670913</v>
+        <v>-3.779366285937871</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-12.77718417244647</v>
       </c>
       <c r="E61">
-        <v>-11.88139102995037</v>
+        <v>-17.14378576309585</v>
       </c>
       <c r="F61">
-        <v>1.816072145294098</v>
+        <v>0.2730152095862347</v>
       </c>
       <c r="G61">
-        <v>-1.07638199567035</v>
+        <v>-4.410253638811242</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-12.9057325080456</v>
       </c>
       <c r="E62">
-        <v>-11.50386573735292</v>
+        <v>-15.57263170613462</v>
       </c>
       <c r="F62">
-        <v>1.398021294795547</v>
+        <v>0.1747723886808217</v>
       </c>
       <c r="G62">
-        <v>-0.903756909070593</v>
+        <v>-3.683966295132693</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-13.02848591442859</v>
       </c>
       <c r="E63">
-        <v>-12.12601466737072</v>
+        <v>-14.10886135331728</v>
       </c>
       <c r="F63">
-        <v>1.400637576967853</v>
+        <v>0.3183693795925896</v>
       </c>
       <c r="G63">
-        <v>-0.9867092486481112</v>
+        <v>-3.939421231125015</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-13.13651711363008</v>
       </c>
       <c r="E64">
-        <v>-10.67233828311647</v>
+        <v>-14.18427403096701</v>
       </c>
       <c r="F64">
-        <v>1.057147600968191</v>
+        <v>0.1212027442381247</v>
       </c>
       <c r="G64">
-        <v>-1.444107462535976</v>
+        <v>-4.048417632459979</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-13.23256285798175</v>
       </c>
       <c r="E65">
-        <v>-11.23319431744045</v>
+        <v>-13.85303427120195</v>
       </c>
       <c r="F65">
-        <v>1.467796210017978</v>
+        <v>-0.4108488010244617</v>
       </c>
       <c r="G65">
-        <v>-2.156076696757176</v>
+        <v>-4.49420576314162</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-13.30943024328849</v>
       </c>
       <c r="E66">
-        <v>-9.997038653670645</v>
+        <v>-14.69609122026193</v>
       </c>
       <c r="F66">
-        <v>1.011064926240734</v>
+        <v>-0.1041174311751072</v>
       </c>
       <c r="G66">
-        <v>-1.026730433672361</v>
+        <v>-4.89547698795668</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-13.36545967187245</v>
       </c>
       <c r="E67">
-        <v>-10.93995751154777</v>
+        <v>-13.82427846125325</v>
       </c>
       <c r="F67">
-        <v>0.9952642923223947</v>
+        <v>-0.8066683797350314</v>
       </c>
       <c r="G67">
-        <v>-2.433381233308688</v>
+        <v>-4.323792120962096</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-13.40110104057122</v>
       </c>
       <c r="E68">
-        <v>-10.58011590995026</v>
+        <v>-14.79061858669804</v>
       </c>
       <c r="F68">
-        <v>0.9259755748160035</v>
+        <v>-0.1468877849804227</v>
       </c>
       <c r="G68">
-        <v>-2.297354227645574</v>
+        <v>-5.009555076694427</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-13.41316342421899</v>
       </c>
       <c r="E69">
-        <v>-11.38805001460675</v>
+        <v>-13.93101006514003</v>
       </c>
       <c r="F69">
-        <v>1.00708665698115</v>
+        <v>-0.4604116695010969</v>
       </c>
       <c r="G69">
-        <v>-1.877904797274375</v>
+        <v>-4.637992687548786</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-13.40943769057212</v>
       </c>
       <c r="E70">
-        <v>-10.44503153030146</v>
+        <v>-13.50116731233196</v>
       </c>
       <c r="F70">
-        <v>0.8954813174142169</v>
+        <v>-0.1152873089967017</v>
       </c>
       <c r="G70">
-        <v>-2.608121758508039</v>
+        <v>-4.692689520948623</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-13.38900357624349</v>
       </c>
       <c r="E71">
-        <v>-9.999126280188181</v>
+        <v>-14.93675697139957</v>
       </c>
       <c r="F71">
-        <v>1.07824414746776</v>
+        <v>-1.120231856903592</v>
       </c>
       <c r="G71">
-        <v>-0.7895894356032869</v>
+        <v>-4.729900052810032</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-13.36406386695657</v>
       </c>
       <c r="E72">
-        <v>-10.52376357939881</v>
+        <v>-13.62162924941</v>
       </c>
       <c r="F72">
-        <v>0.9600030801151354</v>
+        <v>-0.2150338586688244</v>
       </c>
       <c r="G72">
-        <v>-1.532048794241175</v>
+        <v>-4.868936344368343</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-13.33744514093964</v>
       </c>
       <c r="E73">
-        <v>-9.54636492042729</v>
+        <v>-13.6572864537464</v>
       </c>
       <c r="F73">
-        <v>0.8234147797321448</v>
+        <v>0.01249004352574155</v>
       </c>
       <c r="G73">
-        <v>-1.604996665199016</v>
+        <v>-5.193800178137025</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-13.31539628010578</v>
       </c>
       <c r="E74">
-        <v>-9.846118200417015</v>
+        <v>-14.56942980226739</v>
       </c>
       <c r="F74">
-        <v>0.8984776890062283</v>
+        <v>-0.9068678692989698</v>
       </c>
       <c r="G74">
-        <v>-1.214100690104031</v>
+        <v>-4.705891976559237</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-13.30549441069062</v>
       </c>
       <c r="E75">
-        <v>-10.5948968491113</v>
+        <v>-14.08593821789045</v>
       </c>
       <c r="F75">
-        <v>0.4796674515212241</v>
+        <v>-0.9644648778846293</v>
       </c>
       <c r="G75">
-        <v>-1.231726034555111</v>
+        <v>-3.232454231213653</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-13.30644902927993</v>
       </c>
       <c r="E76">
-        <v>-10.52643990753735</v>
+        <v>-14.64184915859805</v>
       </c>
       <c r="F76">
-        <v>0.8071564548042435</v>
+        <v>-1.010283073724208</v>
       </c>
       <c r="G76">
-        <v>-1.36187020079494</v>
+        <v>-3.642213694791405</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-13.3252332781165</v>
       </c>
       <c r="E77">
-        <v>-11.73417033996101</v>
+        <v>-15.02050656969743</v>
       </c>
       <c r="F77">
-        <v>0.8468647132220567</v>
+        <v>-0.2686122134940563</v>
       </c>
       <c r="G77">
-        <v>-0.05558521027269715</v>
+        <v>-3.910079866010455</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-13.35457679560178</v>
       </c>
       <c r="E78">
-        <v>-11.08055304406391</v>
+        <v>-15.09759931120401</v>
       </c>
       <c r="F78">
-        <v>0.840238487671858</v>
+        <v>-1.106420357615044</v>
       </c>
       <c r="G78">
-        <v>-0.2591109289360112</v>
+        <v>-3.241746932542387</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-13.39681518190357</v>
       </c>
       <c r="E79">
-        <v>-11.43171356098871</v>
+        <v>-15.95580400581964</v>
       </c>
       <c r="F79">
-        <v>0.3261026155776804</v>
+        <v>-0.7600844620853378</v>
       </c>
       <c r="G79">
-        <v>-0.1168203711125963</v>
+        <v>-3.537136979374937</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-13.44487705708996</v>
       </c>
       <c r="E80">
-        <v>-12.74491215305101</v>
+        <v>-17.06412537682692</v>
       </c>
       <c r="F80">
-        <v>0.1883487076409264</v>
+        <v>-1.214453648489704</v>
       </c>
       <c r="G80">
-        <v>0.2995767362713944</v>
+        <v>-2.365081368287984</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-13.49598408085397</v>
       </c>
       <c r="E81">
-        <v>-12.35846123818444</v>
+        <v>-17.13868670136321</v>
       </c>
       <c r="F81">
-        <v>0.1007539334579706</v>
+        <v>-1.484521434543677</v>
       </c>
       <c r="G81">
-        <v>0.3771858553485288</v>
+        <v>-4.199649973784966</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-13.5506404876803</v>
       </c>
       <c r="E82">
-        <v>-14.01472343564582</v>
+        <v>-16.49172173378338</v>
       </c>
       <c r="F82">
-        <v>0.2571638970786013</v>
+        <v>-1.506747163360955</v>
       </c>
       <c r="G82">
-        <v>1.598952618253178</v>
+        <v>-2.445805710717573</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-13.60129448233039</v>
       </c>
       <c r="E83">
-        <v>-14.58008983008144</v>
+        <v>-18.61775876785248</v>
       </c>
       <c r="F83">
-        <v>0.2021895054889094</v>
+        <v>-1.639696107550265</v>
       </c>
       <c r="G83">
-        <v>0.8229905387578653</v>
+        <v>-2.152964783950261</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-13.65184132598895</v>
       </c>
       <c r="E84">
-        <v>-14.78302433578718</v>
+        <v>-17.8170339938162</v>
       </c>
       <c r="F84">
-        <v>0.02105868438122668</v>
+        <v>-1.45152017067775</v>
       </c>
       <c r="G84">
-        <v>1.427625265504816</v>
+        <v>-1.401272313803346</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-13.69439533821727</v>
       </c>
       <c r="E85">
-        <v>-16.14926947237533</v>
+        <v>-20.02998150104051</v>
       </c>
       <c r="F85">
-        <v>-0.0271612014791159</v>
+        <v>-1.207414075695576</v>
       </c>
       <c r="G85">
-        <v>2.42988299588255</v>
+        <v>-2.366577734871735</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-13.73227442841847</v>
       </c>
       <c r="E86">
-        <v>-18.04729784015822</v>
+        <v>-19.80565901259655</v>
       </c>
       <c r="F86">
-        <v>-0.1317166741634705</v>
+        <v>-1.526552197686483</v>
       </c>
       <c r="G86">
-        <v>2.106257306145555</v>
+        <v>-1.673849391324778</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-13.76139829854765</v>
       </c>
       <c r="E87">
-        <v>-17.86355953577101</v>
+        <v>-22.58047693232255</v>
       </c>
       <c r="F87">
-        <v>-0.5055678762680219</v>
+        <v>-1.847829114516191</v>
       </c>
       <c r="G87">
-        <v>2.084242178309402</v>
+        <v>-1.414170199224346</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-13.78234720476324</v>
       </c>
       <c r="E88">
-        <v>-20.05032793475697</v>
+        <v>-23.47849597041362</v>
       </c>
       <c r="F88">
-        <v>-0.5824377939916218</v>
+        <v>-1.795869307136538</v>
       </c>
       <c r="G88">
-        <v>2.046482095888475</v>
+        <v>-1.343261624318697</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-13.79977146798225</v>
       </c>
       <c r="E89">
-        <v>-21.47980415391422</v>
+        <v>-25.76120009125208</v>
       </c>
       <c r="F89">
-        <v>-1.05671812301785</v>
+        <v>-2.056241645576191</v>
       </c>
       <c r="G89">
-        <v>2.771309488984205</v>
+        <v>-1.606870433974243</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-13.80961114493253</v>
       </c>
       <c r="E90">
-        <v>-23.74426758144979</v>
+        <v>-26.01383459919199</v>
       </c>
       <c r="F90">
-        <v>-0.9959426166599038</v>
+        <v>-2.563726744678481</v>
       </c>
       <c r="G90">
-        <v>2.268702465212054</v>
+        <v>0.09834522566679524</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-13.81864483168516</v>
       </c>
       <c r="E91">
-        <v>-24.16192421070322</v>
+        <v>-28.05712282771893</v>
       </c>
       <c r="F91">
-        <v>-1.438828351471418</v>
+        <v>-2.498637223406877</v>
       </c>
       <c r="G91">
-        <v>2.131549874065588</v>
+        <v>-1.663815127795247</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-13.82105683785443</v>
       </c>
       <c r="E92">
-        <v>-25.87900381408762</v>
+        <v>-30.38712006685649</v>
       </c>
       <c r="F92">
-        <v>-1.417838705121142</v>
+        <v>-2.454126376800494</v>
       </c>
       <c r="G92">
-        <v>2.311997779774642</v>
+        <v>-2.228561091339519</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-13.81746693288797</v>
       </c>
       <c r="E93">
-        <v>-27.71284559128579</v>
+        <v>-29.77689913737489</v>
       </c>
       <c r="F93">
-        <v>-1.849576733993878</v>
+        <v>-2.906820002346325</v>
       </c>
       <c r="G93">
-        <v>2.434097320354042</v>
+        <v>-1.904644073595069</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-13.80108533302779</v>
       </c>
       <c r="E94">
-        <v>-30.10101560752589</v>
+        <v>-33.42193126478487</v>
       </c>
       <c r="F94">
-        <v>-2.247363275451423</v>
+        <v>-3.321777083339065</v>
       </c>
       <c r="G94">
-        <v>2.078534797799699</v>
+        <v>-2.101290478627778</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-13.76556462787138</v>
       </c>
       <c r="E95">
-        <v>-31.63123905216879</v>
+        <v>-34.85287470952061</v>
       </c>
       <c r="F95">
-        <v>-3.002551857522809</v>
+        <v>-3.197644629981006</v>
       </c>
       <c r="G95">
-        <v>0.1926328731707779</v>
+        <v>-1.470280635569454</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-13.70772847984959</v>
       </c>
       <c r="E96">
-        <v>-33.64809684214995</v>
+        <v>-37.57605670437416</v>
       </c>
       <c r="F96">
-        <v>-3.135342431120575</v>
+        <v>-3.870283333063067</v>
       </c>
       <c r="G96">
-        <v>0.9908087132346004</v>
+        <v>-2.223346982115167</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-13.61854162754543</v>
       </c>
       <c r="E97">
-        <v>-34.69878206022461</v>
+        <v>-37.66807756044702</v>
       </c>
       <c r="F97">
-        <v>-3.014154878912276</v>
+        <v>-4.006788488885497</v>
       </c>
       <c r="G97">
-        <v>0.5429945286829262</v>
+        <v>-2.722875198535796</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-13.49732444835762</v>
       </c>
       <c r="E98">
-        <v>-39.55376357232201</v>
+        <v>-41.65901491069589</v>
       </c>
       <c r="F98">
-        <v>-3.638348809894002</v>
+        <v>-4.180874194228347</v>
       </c>
       <c r="G98">
-        <v>0.7720147585441677</v>
+        <v>-3.437052566631691</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-13.34520563373894</v>
       </c>
       <c r="E99">
-        <v>-41.0105963029596</v>
+        <v>-42.55286548846291</v>
       </c>
       <c r="F99">
-        <v>-4.075203792579524</v>
+        <v>-4.783379272698131</v>
       </c>
       <c r="G99">
-        <v>0.5427561694040987</v>
+        <v>-4.00830375216063</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-13.15834380595189</v>
       </c>
       <c r="E100">
-        <v>-43.70101478836765</v>
+        <v>-45.08706067755434</v>
       </c>
       <c r="F100">
-        <v>-4.455379524257382</v>
+        <v>-4.743982212492702</v>
       </c>
       <c r="G100">
-        <v>0.2757970876628094</v>
+        <v>-3.61280280822052</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.95798048819983</v>
       </c>
       <c r="E101">
-        <v>-44.90674589951693</v>
+        <v>-48.757584717272</v>
       </c>
       <c r="F101">
-        <v>-5.01157941731859</v>
+        <v>-5.297633130883009</v>
       </c>
       <c r="G101">
-        <v>-0.9354984197011252</v>
+        <v>-4.561009261578573</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.73009229607366</v>
       </c>
       <c r="E102">
-        <v>-48.24405236844667</v>
+        <v>-52.21321341931117</v>
       </c>
       <c r="F102">
-        <v>-5.295468204896603</v>
+        <v>-5.272744400568921</v>
       </c>
       <c r="G102">
-        <v>-1.369921447546447</v>
+        <v>-4.991327212955199</v>
       </c>
     </row>
   </sheetData>
